--- a/tabular/reference/sublineage/herv_sublineage_alias.xlsx
+++ b/tabular/reference/sublineage/herv_sublineage_alias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{648AABE7-261C-C641-8B2D-135EE7521A83}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF1C2BD-467A-3242-ABB2-7BF9AB8F6FB6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13520" yWindow="1620" windowWidth="26820" windowHeight="15940" xr2:uid="{E2A31913-0241-5047-ACED-7542084468C7}"/>
+    <workbookView xWindow="9680" yWindow="700" windowWidth="26820" windowHeight="15940" xr2:uid="{E2A31913-0241-5047-ACED-7542084468C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>erv_lineage.id</t>
   </si>
@@ -53,12 +53,6 @@
     <t>repbase</t>
   </si>
   <si>
-    <t>ERV-L47</t>
-  </si>
-  <si>
-    <t>ERVL47</t>
-  </si>
-  <si>
     <t>ERV-Lb4</t>
   </si>
   <si>
@@ -68,12 +62,6 @@
     <t>retrotector</t>
   </si>
   <si>
-    <t>HERV-L74</t>
-  </si>
-  <si>
-    <t>HERVL74</t>
-  </si>
-  <si>
     <t>HUERS-P1</t>
   </si>
   <si>
@@ -89,13 +77,7 @@
     <t>erv_lineage.name</t>
   </si>
   <si>
-    <t>ERV-3.Lambda.47</t>
-  </si>
-  <si>
     <t>ERV-3.Lambda.Lb4</t>
-  </si>
-  <si>
-    <t>ERV-3.Lambda.74</t>
   </si>
   <si>
     <t>ERV-1.Zeta.W9P.P.1</t>
@@ -475,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74414C0-0D01-9B4D-8A37-18FCBAAA5CE9}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.33203125" customWidth="1"/>
@@ -486,7 +468,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -500,7 +482,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
@@ -517,24 +499,24 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>11</v>
@@ -546,41 +528,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
